--- a/output/tables/table_VI_smoothed_hp.xlsx
+++ b/output/tables/table_VI_smoothed_hp.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001435002486734886</v>
+        <v>0.002391076564098408</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004888354067183183</v>
+        <v>0.0007153604353878502</v>
       </c>
       <c r="D2" t="n">
-        <v>2.935553495129246</v>
+        <v>3.34247806534342</v>
       </c>
       <c r="E2" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003429835726392438</v>
+        <v>0.0008705379745754804</v>
       </c>
     </row>
     <row r="3">
@@ -494,85 +494,63 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001372213854275624</v>
+        <v>0.0007588961932858337</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001866506059535542</v>
+        <v>0.00210831155859054</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7351778191478696</v>
+        <v>0.3599544812025672</v>
       </c>
       <c r="E3" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4624577057384163</v>
+        <v>0.7189801349383411</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>S_v</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.04473375570767858</v>
+        <v>-0.002471019255388559</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02281992617426933</v>
+        <v>0.001729210607217521</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.960293620849582</v>
+        <v>-1.428986871278036</v>
       </c>
       <c r="E4" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05032596982094906</v>
+        <v>0.1534146006998995</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S_v</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.002039611798455581</v>
+        <v>-0.016463722054334</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001727008290886485</v>
+        <v>0.01179589581221966</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.18100868954638</v>
+        <v>-1.395716130120344</v>
       </c>
       <c r="E5" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2379682387209803</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.01155100642032743</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.01039499341558409</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-1.111208632706804</v>
-      </c>
-      <c r="E6" t="n">
-        <v>762</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.2668295064549544</v>
+        <v>0.1632033635183991</v>
       </c>
     </row>
   </sheetData>
@@ -586,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,19 +606,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001377425212736574</v>
+        <v>0.002075555987447979</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004719207708986908</v>
+        <v>0.000732139020012827</v>
       </c>
       <c r="D2" t="n">
-        <v>2.918763694408933</v>
+        <v>2.834920596653372</v>
       </c>
       <c r="E2" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003617885348237149</v>
+        <v>0.004708028140356202</v>
       </c>
     </row>
     <row r="3">
@@ -650,85 +628,63 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001782712209442927</v>
+        <v>0.004534931419291454</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002452306436442076</v>
+        <v>0.002190453046022821</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7269532807773287</v>
+        <v>2.07031665322636</v>
       </c>
       <c r="E3" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4674781344887737</v>
+        <v>0.03876715450095647</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>S_v</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.04596535544084902</v>
+        <v>-0.003225438317043544</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02296403307835993</v>
+        <v>0.001619014322073696</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.001623812507233</v>
+        <v>-1.992223461564119</v>
       </c>
       <c r="E4" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04567976117563122</v>
+        <v>0.04671157452758479</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S_v</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001816642368538117</v>
+        <v>-0.01986282586266891</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0015460634024269</v>
+        <v>0.01198446596387513</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.175011558831598</v>
+        <v>-1.657380973214959</v>
       </c>
       <c r="E5" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2403576066364095</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.009829452124577139</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.01042177190843708</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.9431651556890798</v>
-      </c>
-      <c r="E6" t="n">
-        <v>762</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3458957569847938</v>
+        <v>0.09786404642144664</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,19 +740,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00139896070190236</v>
+        <v>0.002229343420783131</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005147612929407816</v>
+        <v>0.0007507484162264034</v>
       </c>
       <c r="D2" t="n">
-        <v>2.717688219932451</v>
+        <v>2.969494670383463</v>
       </c>
       <c r="E2" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006723478221694945</v>
+        <v>0.003078804310676198</v>
       </c>
     </row>
     <row r="3">
@@ -806,19 +762,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003816549186643761</v>
+        <v>0.004640584287777417</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002179130874572241</v>
+        <v>0.002270455861277107</v>
       </c>
       <c r="D3" t="n">
-        <v>1.751408890203963</v>
+        <v>2.04389980308498</v>
       </c>
       <c r="E3" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08027834234504594</v>
+        <v>0.04131508024164687</v>
       </c>
     </row>
     <row r="4">
@@ -828,85 +784,63 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.71303743288391e-06</v>
+        <v>0.0002825650902724974</v>
       </c>
       <c r="C4" t="n">
-        <v>7.619784826803497e-06</v>
+        <v>0.0001308067844524454</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4872890137032296</v>
+        <v>2.160171519048566</v>
       </c>
       <c r="E4" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.62619386549603</v>
+        <v>0.03107807327523004</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>S_v</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.04308288904608475</v>
+        <v>-0.003582150700201154</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02336736078137091</v>
+        <v>0.001654805195721543</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.843720797105662</v>
+        <v>-2.164696309549133</v>
       </c>
       <c r="E5" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0656124520544703</v>
+        <v>0.03072828564603625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S_v</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001893755765436276</v>
+        <v>-0.007027441682015061</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001536280466711597</v>
+        <v>0.01394521712701316</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.232688826337715</v>
+        <v>-0.5039320376304693</v>
       </c>
       <c r="E6" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2180725566741846</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-0.01055493986138404</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.01058291396871026</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.9973566725186539</v>
-      </c>
-      <c r="E7" t="n">
-        <v>762</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.3189084328353542</v>
+        <v>0.6144583207028311</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,19 +896,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001507129591994048</v>
+        <v>0.002589041094402576</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004287442940777117</v>
+        <v>0.0007314699496309186</v>
       </c>
       <c r="D2" t="n">
-        <v>3.515217841525081</v>
+        <v>3.539504385257304</v>
       </c>
       <c r="E2" t="n">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004653908912954918</v>
+        <v>0.0004250359112591973</v>
       </c>
     </row>
     <row r="3">
@@ -984,85 +918,63 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006430407019889104</v>
+        <v>0.001267351222929986</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001932298334196516</v>
+        <v>0.002139116932402277</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3327854144511791</v>
+        <v>0.5924646772379675</v>
       </c>
       <c r="E3" t="n">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7393879222537461</v>
+        <v>0.5537140854868592</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>S_v</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07775173912746387</v>
+        <v>-0.003408623498782155</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02377304013819391</v>
+        <v>0.001758913555830679</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.270584606574885</v>
+        <v>-1.937914167232835</v>
       </c>
       <c r="E4" t="n">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001121572879932087</v>
+        <v>0.05300039189400585</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S_v</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.002346707932510584</v>
+        <v>-0.001839767369318666</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00173924523763995</v>
+        <v>0.01142975435847785</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.349267993796507</v>
+        <v>-0.1609629841217056</v>
       </c>
       <c r="E5" t="n">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1776521904578527</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.01680874223349963</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.01085409380038471</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.548608528968477</v>
-      </c>
-      <c r="E6" t="n">
-        <v>762</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1218915996256376</v>
+        <v>0.872164940705531</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,19 +1030,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001377068395178782</v>
+        <v>0.002449157996928817</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004225611509284408</v>
+        <v>0.0007557641396068054</v>
       </c>
       <c r="D2" t="n">
-        <v>3.258861805334261</v>
+        <v>3.24063800937025</v>
       </c>
       <c r="E2" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001168286564746657</v>
+        <v>0.001245767414095988</v>
       </c>
     </row>
     <row r="3">
@@ -1140,85 +1052,63 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003813573820514984</v>
+        <v>0.003511773336770065</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002574575276548625</v>
+        <v>0.002216060514616428</v>
       </c>
       <c r="D3" t="n">
-        <v>1.481243860007586</v>
+        <v>1.584691985443325</v>
       </c>
       <c r="E3" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1389555162869938</v>
+        <v>0.1134618362811914</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>S_v</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07959552048519655</v>
+        <v>-0.004031452246681519</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0238492076669386</v>
+        <v>0.001605149419552301</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.337449260234221</v>
+        <v>-2.511574435111435</v>
       </c>
       <c r="E4" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000886592675285458</v>
+        <v>0.01223041640487166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S_v</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.003000957168794454</v>
+        <v>-0.008012203277869745</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001486402599556865</v>
+        <v>0.01143039173390132</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0189396666079</v>
+        <v>-0.7009561408211763</v>
       </c>
       <c r="E5" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04384370087761091</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.01667111175315157</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.01077597281477323</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.547063271196866</v>
-      </c>
-      <c r="E6" t="n">
-        <v>762</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1222637277963616</v>
+        <v>0.4835498464697869</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1274,19 +1164,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001557330510221606</v>
+        <v>0.002398643704332388</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004710798160171154</v>
+        <v>0.0007637529391513872</v>
       </c>
       <c r="D2" t="n">
-        <v>3.305873988379551</v>
+        <v>3.140601602132678</v>
       </c>
       <c r="E2" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009911892746536921</v>
+        <v>0.001752823338913245</v>
       </c>
     </row>
     <row r="3">
@@ -1296,19 +1186,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003405307476363214</v>
+        <v>0.003753002062385146</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002766347451889077</v>
+        <v>0.002265981968058099</v>
       </c>
       <c r="D3" t="n">
-        <v>1.230976056184774</v>
+        <v>1.656236508184305</v>
       </c>
       <c r="E3" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2187121300457833</v>
+        <v>0.09809615140903327</v>
       </c>
     </row>
     <row r="4">
@@ -1318,85 +1208,63 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.000805542845506e-05</v>
+        <v>0.0003496006885053994</v>
       </c>
       <c r="C4" t="n">
-        <v>8.182330237442503e-06</v>
+        <v>0.0001285751301757877</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.223130225502022</v>
+        <v>2.719038184347362</v>
       </c>
       <c r="E4" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2216591352748014</v>
+        <v>0.006699999269638379</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>S_v</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.08753870454905542</v>
+        <v>-0.003624170680147746</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02405302788003629</v>
+        <v>0.001622056797093823</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.639404776215781</v>
+        <v>-2.234305658495456</v>
       </c>
       <c r="E5" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002917381228093596</v>
+        <v>0.02575964276334508</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S_v</t>
+          <t>Ret</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.003025620178371164</v>
+        <v>0.009628199095096551</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001517545525851809</v>
+        <v>0.0129441186953334</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.993759084540717</v>
+        <v>0.7438280907117837</v>
       </c>
       <c r="E6" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04653488309234621</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ret</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.01835014669148486</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.01098131756026687</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.67103324266664</v>
-      </c>
-      <c r="E7" t="n">
-        <v>762</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.09512625991400481</v>
+        <v>0.4572156385028605</v>
       </c>
     </row>
   </sheetData>
